--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,536 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131915069</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79885</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>682374</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7397458</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131915072</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79856</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>682343</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7397482</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131915070</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79856</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>682412</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7397430</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131915068</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78669</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>682410</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7397431</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131915073</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78273</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>682380</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7397525</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>131915069</v>
       </c>
       <c r="B5" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131915072</v>
       </c>
       <c r="B6" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>131915070</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>131915068</v>
       </c>
       <c r="B8" t="n">
-        <v>78669</v>
+        <v>78672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131915073</v>
       </c>
       <c r="B9" t="n">
-        <v>78273</v>
+        <v>78276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>131915069</v>
       </c>
       <c r="B5" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131915072</v>
       </c>
       <c r="B6" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>131915070</v>
       </c>
       <c r="B7" t="n">
-        <v>79859</v>
+        <v>79864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>131915068</v>
       </c>
       <c r="B8" t="n">
-        <v>78672</v>
+        <v>78677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131915073</v>
       </c>
       <c r="B9" t="n">
-        <v>78276</v>
+        <v>78281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>131915069</v>
       </c>
       <c r="B5" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131915072</v>
       </c>
       <c r="B6" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>131915070</v>
       </c>
       <c r="B7" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>131915068</v>
       </c>
       <c r="B8" t="n">
-        <v>78677</v>
+        <v>78679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131915073</v>
       </c>
       <c r="B9" t="n">
-        <v>78281</v>
+        <v>78283</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>131915069</v>
       </c>
       <c r="B5" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131915072</v>
       </c>
       <c r="B6" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>131915070</v>
       </c>
       <c r="B7" t="n">
-        <v>79905</v>
+        <v>79907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>131915068</v>
       </c>
       <c r="B8" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131915073</v>
       </c>
       <c r="B9" t="n">
-        <v>78322</v>
+        <v>78324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>131915069</v>
       </c>
       <c r="B5" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131915072</v>
       </c>
       <c r="B6" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>131915070</v>
       </c>
       <c r="B7" t="n">
-        <v>79907</v>
+        <v>79909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>131915068</v>
       </c>
       <c r="B8" t="n">
-        <v>78720</v>
+        <v>78722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131915073</v>
       </c>
       <c r="B9" t="n">
-        <v>78324</v>
+        <v>78326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>131915069</v>
       </c>
       <c r="B5" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>131915072</v>
       </c>
       <c r="B6" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>131915070</v>
       </c>
       <c r="B7" t="n">
-        <v>79909</v>
+        <v>79917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>131915068</v>
       </c>
       <c r="B8" t="n">
-        <v>78722</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131915073</v>
       </c>
       <c r="B9" t="n">
-        <v>78326</v>
+        <v>78334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128078116</v>
+        <v>128078070</v>
       </c>
       <c r="B2" t="n">
-        <v>78847</v>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682440</v>
+        <v>682387</v>
       </c>
       <c r="R2" t="n">
-        <v>7397416</v>
+        <v>7397426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128078123</v>
+        <v>131915068</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>78776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Áhkehávrre, Áhkehávrre, Lu lm</t>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682440</v>
+        <v>682410</v>
       </c>
       <c r="R3" t="n">
-        <v>7397416</v>
+        <v>7397431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,28 +854,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128078070</v>
+        <v>131915069</v>
       </c>
       <c r="B4" t="n">
-        <v>79168</v>
+        <v>79992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Áhkehávrre, Áhkehávrre, Lu lm</t>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682387</v>
+        <v>682374</v>
       </c>
       <c r="R4" t="n">
-        <v>7397426</v>
+        <v>7397458</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -948,28 +960,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Rashid Kadhim, Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131915069</v>
+        <v>131915073</v>
       </c>
       <c r="B5" t="n">
-        <v>79946</v>
+        <v>78377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +995,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1004,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>682374</v>
+        <v>682380</v>
       </c>
       <c r="R5" t="n">
-        <v>7397458</v>
+        <v>7397525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,48 +1090,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131915072</v>
+        <v>110045485</v>
       </c>
       <c r="B6" t="n">
-        <v>79917</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+          <t>Rakalvis C, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682343</v>
+        <v>682287</v>
       </c>
       <c r="R6" t="n">
-        <v>7397482</v>
+        <v>7397443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1140,12 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1154,34 +1169,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131915070</v>
+        <v>128078116</v>
       </c>
       <c r="B7" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,37 +1198,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+          <t>Áhkehávrre, Áhkehávrre, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>682412</v>
+        <v>682440</v>
       </c>
       <c r="R7" t="n">
-        <v>7397430</v>
+        <v>7397416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,34 +1266,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131915068</v>
+        <v>128078123</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>79917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,37 +1295,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+          <t>Áhkehávrre, Áhkehávrre, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>682410</v>
+        <v>682440</v>
       </c>
       <c r="R8" t="n">
-        <v>7397431</v>
+        <v>7397416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,12 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1366,34 +1363,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Alexander Singer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131915073</v>
+        <v>131915070</v>
       </c>
       <c r="B9" t="n">
-        <v>78334</v>
+        <v>79963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1392,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>682380</v>
+        <v>682412</v>
       </c>
       <c r="R9" t="n">
-        <v>7397525</v>
+        <v>7397430</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,6 +1484,324 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131915072</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>682343</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7397482</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131915067</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>682369</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7397517</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131915071</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skog norr om Piertinjaure, SO om Ákhehávrre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>682396</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7397448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Flerskiktad, löv-och hänglavsrik barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3509-2026 artfynd.xlsx
+++ b/artfynd/A 3509-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915068</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045485</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078116</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078123</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915070</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915072</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915067</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1802,8 +1857,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131915071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>